--- a/Output/heterog_terciles_migration_lapop.xlsx
+++ b/Output/heterog_terciles_migration_lapop.xlsx
@@ -456,40 +456,40 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0313111150237111</v>
+        <v>-0.031311115023667</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0521016483637515</v>
+        <v>0.0520995937926193</v>
       </c>
       <c r="E2" t="n">
-        <v>0.547865242511033</v>
+        <v>0.547849457424598</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.141376063343207</v>
+        <v>-0.14137606334345</v>
       </c>
       <c r="G2" t="n">
-        <v>0.267255048078854</v>
+        <v>0.26728999960266</v>
       </c>
       <c r="H2" t="n">
-        <v>0.596810270263571</v>
+        <v>0.596858256453463</v>
       </c>
       <c r="I2" t="n">
-        <v>0.69071614133107</v>
+        <v>0.690752161836675</v>
       </c>
       <c r="J2" t="n">
         <v>1936</v>
       </c>
       <c r="K2" t="n">
-        <v>0.149925595205259</v>
+        <v>0.149925595205278</v>
       </c>
       <c r="L2" t="n">
         <v>0.0972222222222222</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0540205533547348</v>
+        <v>0.0540110836206218</v>
       </c>
       <c r="N2" t="n">
-        <v>0.565099619107665</v>
+        <v>0.565175191590901</v>
       </c>
     </row>
     <row r="3">
@@ -500,40 +500,40 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0348200629703612</v>
+        <v>0.0348200629703654</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0139208909724463</v>
+        <v>0.0139204118978506</v>
       </c>
       <c r="E3" t="n">
-        <v>0.012374487765202</v>
+        <v>0.0123714799910768</v>
       </c>
       <c r="F3" t="n">
-        <v>0.14458970594611</v>
+        <v>0.144589705946116</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0612225863548626</v>
+        <v>0.061225361604004</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0181910970956685</v>
+        <v>0.0181963502428383</v>
       </c>
       <c r="I3" t="n">
-        <v>0.134454188558093</v>
+        <v>0.134466267983532</v>
       </c>
       <c r="J3" t="n">
         <v>2841</v>
       </c>
       <c r="K3" t="n">
-        <v>0.147745177957946</v>
+        <v>0.147745177957964</v>
       </c>
       <c r="L3" t="n">
         <v>0.157534246575342</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0540205533547348</v>
+        <v>0.0540110836206218</v>
       </c>
       <c r="N3" t="n">
-        <v>0.565099619107665</v>
+        <v>0.565175191590901</v>
       </c>
     </row>
     <row r="4">
@@ -544,40 +544,40 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.075567936799841</v>
+        <v>-0.0755679367998054</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0491049345543727</v>
+        <v>0.0491036225566848</v>
       </c>
       <c r="E4" t="n">
-        <v>0.123826955876642</v>
+        <v>0.123816916597972</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0949835654227785</v>
+        <v>0.0949835654228457</v>
       </c>
       <c r="G4" t="n">
-        <v>0.140424212338567</v>
+        <v>0.140421820683836</v>
       </c>
       <c r="H4" t="n">
-        <v>0.498783877739547</v>
+        <v>0.498776565357351</v>
       </c>
       <c r="I4" t="n">
-        <v>0.363163378372507</v>
+        <v>0.363154247297824</v>
       </c>
       <c r="J4" t="n">
         <v>2635</v>
       </c>
       <c r="K4" t="n">
-        <v>0.132696257599554</v>
+        <v>0.132696257599542</v>
       </c>
       <c r="L4" t="n">
         <v>0.277777777777778</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0540205533547348</v>
+        <v>0.0540110836206218</v>
       </c>
       <c r="N4" t="n">
-        <v>0.565099619107665</v>
+        <v>0.565175191590901</v>
       </c>
     </row>
     <row r="5">
@@ -588,40 +588,40 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0268749454962364</v>
+        <v>0.0268749454962593</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0437195866281894</v>
+        <v>0.0437215912581577</v>
       </c>
       <c r="E5" t="n">
-        <v>0.538745070119272</v>
+        <v>0.538763686706246</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0604756512811738</v>
+        <v>-0.0604756512812491</v>
       </c>
       <c r="G5" t="n">
-        <v>0.125311508251221</v>
+        <v>0.125328818154747</v>
       </c>
       <c r="H5" t="n">
-        <v>0.629377980327725</v>
+        <v>0.629425317860611</v>
       </c>
       <c r="I5" t="n">
-        <v>0.597601437147417</v>
+        <v>0.597649810775044</v>
       </c>
       <c r="J5" t="n">
         <v>2556</v>
       </c>
       <c r="K5" t="n">
-        <v>0.128068244104222</v>
+        <v>0.12806824410425</v>
       </c>
       <c r="L5" t="n">
         <v>0.493150684931507</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0808610806524438</v>
+        <v>0.0808533112793408</v>
       </c>
       <c r="N5" t="n">
-        <v>0.326266094835077</v>
+        <v>0.326330276319983</v>
       </c>
     </row>
     <row r="6">
@@ -632,40 +632,40 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0434288042017894</v>
+        <v>0.043428804201783</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0233407184616614</v>
+        <v>0.0233415084328464</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0627942462686691</v>
+        <v>0.0628031453940814</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0317144722420516</v>
+        <v>0.0317144722420284</v>
       </c>
       <c r="G6" t="n">
-        <v>0.103295695340653</v>
+        <v>0.103307740866403</v>
       </c>
       <c r="H6" t="n">
-        <v>0.758823522650677</v>
+        <v>0.758850771064387</v>
       </c>
       <c r="I6" t="n">
-        <v>0.924396535699198</v>
+        <v>0.924404392190365</v>
       </c>
       <c r="J6" t="n">
         <v>3103</v>
       </c>
       <c r="K6" t="n">
-        <v>0.159886052299303</v>
+        <v>0.159886052299324</v>
       </c>
       <c r="L6" t="n">
         <v>0.545706371191136</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0808610806524438</v>
+        <v>0.0808533112793408</v>
       </c>
       <c r="N6" t="n">
-        <v>0.326266094835077</v>
+        <v>0.326330276319983</v>
       </c>
     </row>
     <row r="7">
@@ -676,40 +676,40 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0722810688353088</v>
+        <v>-0.0722810688353083</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0461320736652741</v>
+        <v>0.0461306370816208</v>
       </c>
       <c r="E7" t="n">
-        <v>0.117154677116565</v>
+        <v>0.117143269359837</v>
       </c>
       <c r="F7" t="n">
-        <v>0.243830510295645</v>
+        <v>0.24383051029561</v>
       </c>
       <c r="G7" t="n">
-        <v>0.161503688247698</v>
+        <v>0.161514222216813</v>
       </c>
       <c r="H7" t="n">
-        <v>0.13110672672315</v>
+        <v>0.131131863201817</v>
       </c>
       <c r="I7" t="n">
-        <v>0.118699151079168</v>
+        <v>0.118718979799297</v>
       </c>
       <c r="J7" t="n">
         <v>1753</v>
       </c>
       <c r="K7" t="n">
-        <v>0.127274762277712</v>
+        <v>0.127274762277697</v>
       </c>
       <c r="L7" t="n">
         <v>0.684931506849315</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0808610806524438</v>
+        <v>0.0808533112793408</v>
       </c>
       <c r="N7" t="n">
-        <v>0.326266094835077</v>
+        <v>0.326330276319983</v>
       </c>
     </row>
   </sheetData>
